--- a/task1-job-outreach/sheet-template/RAY_Lead_Engine_Template.xlsx
+++ b/task1-job-outreach/sheet-template/RAY_Lead_Engine_Template.xlsx
@@ -722,7 +722,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="I2:I2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"New,Contacted,Replied,Won,Lost"</formula1>
+      <formula1>"New,Contacted,Replied,Won,Lost,Expired"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
